--- a/site/exports/sdu-math.xlsx
+++ b/site/exports/sdu-math.xlsx
@@ -452,8 +452,8 @@
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">

--- a/site/exports/sdu-math.xlsx
+++ b/site/exports/sdu-math.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -675,12 +675,66 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>王志伟</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>数学学院</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Official personal-page affiliation supports partial candidate; independent directory and current employment unverified.；Three study/degree labels remain degree_awarded unknown; graduation labels and interval ends are not explicit conferral dates.；Overlapping master and doctorate intervals retained, no invented explanation.；Own mentor identities unknown; doctoral supervisor title is not an own-advisor relationship.；Two selected source-reported works only; publisher metadata and full texts not independently verified.；Page creation and update dates are not verified by the retained excerpts.；来源差异/限制：Master 2012-09 to2015-06 and doctorate2014-09 to2018-03 overlap as source lists; not reconciled.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -692,13 +746,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="29.4" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="61.59999999999999" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -774,7 +828,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -2527,8 +2581,406 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>王志伟</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>理学博士学位</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>法国洛林大学</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>解析数论</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>王志伟</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>理学硕士学位</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2015-06</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>基础数学</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>王志伟</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>理学学士学位</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2008-09</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2012-06</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>数学与应用数学</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>王志伟</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>山东大学数学学院</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>王志伟</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>加拿大蒙特利尔大学 Centre de Recherches Mathématiques</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>王志伟</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>山东大学数学学院</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S25"/>
+  <autoFilter ref="A1:S31"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -2554,6 +3006,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2811,7 +3269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2823,7 +3281,7 @@
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="26.6" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -3002,8 +3460,108 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>王志伟</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Averaged forms of two conjectures of Erdős and Pomerance, and their applications</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/lwcg/1346931/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/lwcg/1346931/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：蒋玉蛟、吕广世、王志伟；来源书目信息（文章编号）：108592；来源书目信息（length_as_source）：42 pp.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>王志伟</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Averages of coeffients of a class of degree 3 L-functions</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/lwcg/1346931/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/lwcg/1346931/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：黄炳荣、林永晓、王志伟；来源书目信息（卷）：57；来源书目信息（页码）：79--91</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -3011,6 +3569,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3022,14 +3584,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="39.2" customWidth="1" min="2" max="2"/>
+    <col width="62.99999999999999" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3444,27 +4006,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>刘建亚</t>
+          <t>王志伟</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>institution-classification-5</t>
+          <t>new-recovery-sdu-wangzhiwei-s001-a9cc352a23fc</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</t>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>未单独记录</t>
+          <t>2026-10-25T05:37:20Z</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3481,27 +4043,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>胡锡俊</t>
+          <t>王志伟</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>institution-classification-2</t>
+          <t>new-recovery-sdu-wangzhiwei-s002-d45b8a6787ec</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>https://www.jlu.edu.cn/xxgk.htm</t>
+          <t>https://faculty.sdu.edu.cn/wangzhiwei1/zh_CN/lwcg/1346931/list/index.htm</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>未单独记录</t>
+          <t>2026-10-25T05:37:24Z</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3518,42 +4080,116 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>刘建亚</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>institution-classification-5</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>未单独记录</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>胡锡俊</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>institution-classification-2</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jlu.edu.cn/xxgk.htm</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>未单独记录</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>张晓燕</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>institution-classification-3</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>未单独记录</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>sdu</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>山东大学</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -3568,6 +4204,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/sdu-math.xlsx
+++ b/site/exports/sdu-math.xlsx
@@ -2691,7 +2691,7 @@
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
@@ -2760,7 +2760,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
